--- a/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
+++ b/InputData/indst/SoCiIEPTtB/Shr of Cng in Indst Expenses Passed Thr to Buyers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\WA\indst\SoCiIEPTtB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\indst\SoCiIEPTtB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9C41DB7-BD30-40F1-9444-2B4F5EF74EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D87643-3FBD-4818-AB4B-E532AC1F3B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="335" yWindow="335" windowWidth="12185" windowHeight="7455" activeTab="1" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
+    <workbookView xWindow="35730" yWindow="4035" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{C45C27AA-02D4-49AC-94B3-A048BBC9260E}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>SoCiIEPTtB Share of Change in Industry Expenses Passed Through to Buyers</t>
   </si>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>construction 41T43</t>
-  </si>
-  <si>
-    <t>Washington</t>
   </si>
 </sst>
 </file>
@@ -277,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -285,7 +282,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -601,24 +597,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA9904B-1EB4-4402-820D-BB1B47048552}">
-  <dimension ref="A1:C42"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="91.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="5">
-        <v>45450</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -626,157 +616,157 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1</v>
       </c>
@@ -799,13 +789,13 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.54296875" customWidth="1"/>
     <col min="2" max="2" width="16.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -813,7 +803,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -822,7 +812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -831,7 +821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -840,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -849,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -858,7 +848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -867,7 +857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -876,7 +866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -885,7 +875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -894,7 +884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -903,7 +893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -912,7 +902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -921,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -930,7 +920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -939,7 +929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -948,7 +938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -957,7 +947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -966,7 +956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -975,7 +965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -984,7 +974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -993,7 +983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -1002,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>56</v>
       </c>
@@ -1011,7 +1001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1020,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>58</v>
       </c>
@@ -1029,7 +1019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>59</v>
       </c>
